--- a/src/web/ltodm-web/public/assets/templates/style-library-import-template.xlsx
+++ b/src/web/ltodm-web/public/assets/templates/style-library-import-template.xlsx
@@ -19,9 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -69,16 +68,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -464,6 +464,8 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,6 +554,16 @@
           <t>Image</t>
         </is>
       </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Cust_Name</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Customer_Brand</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -622,8 +634,18 @@
           <t>Training</t>
         </is>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="7" t="n">
         <v>46175.43164351852</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>adidas</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ADIDAS</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -738,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -763,6 +785,7 @@
     <col width="15" customWidth="1" min="20" max="20"/>
     <col width="17" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -876,6 +899,11 @@
           <t>Image</t>
         </is>
       </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Consump_Allowance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -976,6 +1004,9 @@
         <is>
           <t>NO COLOR</t>
         </is>
+      </c>
+      <c r="W2" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -989,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1002,11 +1033,6 @@
           <t>Style Library import template</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1016,7 +1042,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Keep the first three sheets in this order: Style Header, Article (colorways), BOM Detail. This sheet is ignored.</t>
+          <t>Keep three sheets: Style Header, Article (colorways), BOM Detail. Other sheet names and headings can be used: after choosing the file you map each sheet and column (and can save the mapping for the next file). This sheet is ignored.</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1066,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Cust + Season_ID + Style_ID identifies a style. Season_ID looks like 2027-SS (terms SP, SS, SU, FA, FW, WI).</t>
+          <t>Cust + Season_ID + Style_ID identifies a style (Style_ID and Article ID up to 100 characters). Season_ID is kept as written: 2027-SS (terms SP, SS, SU, FA, FW, WI) or the source system's name (26FW, FA26); a new season can be pointed at an existing one on the New codes tab.</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1102,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>One row per BOM line per colorway (Article ID must be on the Article sheet for the same style). Content_Class: FAB, TRI, ACC, LNP or ART.</t>
+          <t>One row per BOM line per colorway (Article ID must be on the Article sheet for the same style); a row without an Article ID applies to all of the style's colorways. Content_Class: FAB, TRI, ACC, LNP or ART.</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1114,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>LCO_Consump and AD_Consump are numbers; blank or NULL means not given. UOM is folded to lower case (PC = pc).</t>
+          <t>LCO_Consump, AD_Consump and Consump_Allowance are numbers; blank or NULL means not given. UOM is folded to lower case (PC = pc).</t>
         </is>
       </c>
     </row>
@@ -1113,6 +1139,30 @@
       <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Styles already in the library show as Changed or Unchanged. Only the Changed styles you tick are replaced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Cust_Name</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Optional: the customer account name. Kept on each style and used as the name of a customer the import adds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Customer_Brand</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Optional: the brand of the customer account. Accounts of one brand stay separate customers but are grouped (several POLO accounts -&gt; POLO).</t>
         </is>
       </c>
     </row>
